--- a/data/trans_bre/P19C05-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P19C05-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 7,24</t>
+          <t>-1,69; 7,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 9,62</t>
+          <t>1,15; 10,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 5,08</t>
+          <t>-4,62; 5,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,29; 11,97</t>
+          <t>4,64; 12,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 29,7</t>
+          <t>-5,71; 29,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 37,51</t>
+          <t>3,8; 40,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-20,15; 27,69</t>
+          <t>-20,25; 31,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,17; 75,56</t>
+          <t>21,66; 83,42</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 3,04</t>
+          <t>-1,16; 3,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 2,05</t>
+          <t>-2,72; 2,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 2,76</t>
+          <t>-1,38; 2,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 2,01</t>
+          <t>-2,93; 2,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-17,18; 47,93</t>
+          <t>-13,42; 53,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,03; 21,66</t>
+          <t>-23,56; 21,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,88; 35,96</t>
+          <t>-14,3; 33,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,91; 30,46</t>
+          <t>-32,72; 29,08</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 2,94</t>
+          <t>-5,37; 3,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 2,61</t>
+          <t>-5,55; 2,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 2,87</t>
+          <t>-4,18; 2,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 1,28</t>
+          <t>-3,98; 1,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-42,32; 34,35</t>
+          <t>-41,07; 40,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,33; 44,07</t>
+          <t>-49,24; 42,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-41,96; 51,51</t>
+          <t>-43,19; 49,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-41,02; 19,23</t>
+          <t>-40,57; 22,04</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,66</t>
+          <t>0,56; 4,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 5,25</t>
+          <t>1,24; 5,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,67</t>
+          <t>-0,86; 2,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 3,86</t>
+          <t>-0,51; 3,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,4; 36,38</t>
+          <t>3,47; 34,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,69; 38,1</t>
+          <t>7,62; 36,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 27,67</t>
+          <t>-7,77; 26,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 47,65</t>
+          <t>-4,09; 49,32</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C05-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P19C05-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,51</t>
+          <t>8,81</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>49,98%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 7,36</t>
+          <t>-1,5; 7,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 10,12</t>
+          <t>1,24; 9,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 5,64</t>
+          <t>-4,36; 5,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,64; 12,92</t>
+          <t>4,87; 12,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 29,65</t>
+          <t>-4,81; 30,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,8; 40,6</t>
+          <t>3,43; 39,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 31,23</t>
+          <t>-18,88; 29,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,66; 83,42</t>
+          <t>24,26; 81,45</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,83</t>
+          <t>-0,82</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-10,44%</t>
+          <t>-8,87%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 3,32</t>
+          <t>-1,21; 3,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 2,09</t>
+          <t>-2,57; 1,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 2,58</t>
+          <t>-1,48; 2,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 2,22</t>
+          <t>-2,63; 0,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 53,53</t>
+          <t>-13,3; 48,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,56; 21,81</t>
+          <t>-21,66; 21,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,3; 33,85</t>
+          <t>-14,46; 35,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,72; 29,08</t>
+          <t>-24,64; 7,19</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,42</t>
+          <t>-1,4</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-16,73%</t>
+          <t>-16,85%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 3,32</t>
+          <t>-5,58; 2,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 2,82</t>
+          <t>-5,18; 2,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 2,85</t>
+          <t>-4,0; 3,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 1,51</t>
+          <t>-3,91; 1,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-41,07; 40,43</t>
+          <t>-43,25; 33,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,24; 42,93</t>
+          <t>-46,05; 46,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-43,19; 49,56</t>
+          <t>-43,98; 52,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-40,57; 22,04</t>
+          <t>-39,82; 15,52</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,53</t>
+          <t>1,64</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,36</t>
+          <t>0,46; 4,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,16</t>
+          <t>1,17; 5,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 2,6</t>
+          <t>-0,75; 2,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 3,9</t>
+          <t>0,25; 2,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,47; 34,08</t>
+          <t>3,27; 35,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,62; 36,94</t>
+          <t>7,1; 36,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 26,42</t>
+          <t>-6,41; 27,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 49,32</t>
+          <t>2,52; 31,23</t>
         </is>
       </c>
     </row>
